--- a/tams-invest-parent/tams-invest-asset/src/main/resources/tpl/SppiTest001_2.xlsx
+++ b/tams-invest-parent/tams-invest-asset/src/main/resources/tpl/SppiTest001_2.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cms\tams\tams-invest-parent\tams-invest-asset\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7130"/>
   </bookViews>
   <sheets>
     <sheet name="中债SPPI结果导入模板" sheetId="2" r:id="rId1"/>
@@ -73,6 +78,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1.导入模板sheet页中字体为</t>
@@ -82,6 +88,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>红色</t>
@@ -90,6 +97,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>的是</t>
@@ -99,6 +107,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>必填</t>
@@ -107,6 +116,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>字段,非红色字体字段为非必填或者是条件必填</t>
@@ -122,14 +132,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +146,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -150,166 +155,48 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,198 +205,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -532,345 +233,62 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1128,26 +546,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G119"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="8" customWidth="1"/>
-    <col min="2" max="2" width="18.3727272727273" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.6272727272727" style="8" customWidth="1"/>
-    <col min="4" max="4" width="26.7545454545455" style="8" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="9" customWidth="1"/>
-    <col min="6" max="6" width="9.12727272727273" style="8" customWidth="1"/>
-    <col min="7" max="7" width="21.6272727272727" style="8" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.6328125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="26.7265625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="24.453125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="8" customWidth="1"/>
+    <col min="7" max="7" width="21.6328125" style="8" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1170,16 +588,16 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="11"/>
+      <c r="E2" s="12"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1188,7 +606,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1197,385 +615,391 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="3:3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C5" s="5"/>
     </row>
-    <row r="6" spans="3:3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C6" s="5"/>
     </row>
-    <row r="7" spans="3:3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C7" s="5"/>
     </row>
-    <row r="8" spans="3:3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C8" s="5"/>
     </row>
-    <row r="9" spans="3:3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C9" s="5"/>
     </row>
-    <row r="10" spans="3:3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C10" s="5"/>
     </row>
-    <row r="11" spans="3:3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C11" s="5"/>
     </row>
-    <row r="12" spans="3:3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C12" s="5"/>
     </row>
-    <row r="13" spans="3:3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C13" s="5"/>
     </row>
-    <row r="14" spans="3:3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C14" s="5"/>
     </row>
-    <row r="15" spans="3:3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C15" s="5"/>
     </row>
-    <row r="16" spans="3:3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C16" s="5"/>
     </row>
-    <row r="17" spans="3:3">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" s="5"/>
     </row>
-    <row r="18" spans="3:3">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C18" s="5"/>
     </row>
-    <row r="19" spans="3:3">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C19" s="5"/>
     </row>
-    <row r="20" spans="3:3">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C20" s="5"/>
     </row>
-    <row r="21" spans="3:3">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C21" s="5"/>
     </row>
-    <row r="22" spans="3:3">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C22" s="5"/>
     </row>
-    <row r="23" spans="3:3">
+    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C23" s="5"/>
     </row>
-    <row r="24" spans="3:3">
+    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C24" s="5"/>
     </row>
-    <row r="25" spans="3:3">
+    <row r="25" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C25" s="5"/>
     </row>
-    <row r="26" spans="3:3">
+    <row r="26" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C26" s="5"/>
     </row>
-    <row r="27" spans="3:3">
+    <row r="27" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C27" s="5"/>
     </row>
-    <row r="28" spans="3:3">
+    <row r="28" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C28" s="5"/>
     </row>
-    <row r="29" spans="3:3">
+    <row r="29" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C29" s="5"/>
     </row>
-    <row r="30" spans="3:3">
+    <row r="30" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C30" s="5"/>
     </row>
-    <row r="31" spans="3:3">
+    <row r="31" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C31" s="5"/>
     </row>
-    <row r="32" spans="3:3">
+    <row r="32" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C32" s="5"/>
     </row>
-    <row r="33" spans="3:3">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" s="5"/>
     </row>
-    <row r="34" spans="3:3">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C34" s="5"/>
     </row>
-    <row r="35" spans="3:3">
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C35" s="5"/>
     </row>
-    <row r="36" spans="3:3">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C36" s="5"/>
     </row>
-    <row r="37" spans="3:3">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C37" s="5"/>
     </row>
-    <row r="38" spans="3:3">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C38" s="5"/>
     </row>
-    <row r="39" spans="3:3">
+    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C39" s="5"/>
     </row>
-    <row r="40" spans="3:3">
+    <row r="40" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C40" s="5"/>
     </row>
-    <row r="41" spans="3:3">
+    <row r="41" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C41" s="5"/>
     </row>
-    <row r="42" spans="3:3">
+    <row r="42" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C42" s="5"/>
     </row>
-    <row r="43" spans="3:3">
+    <row r="43" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C43" s="5"/>
     </row>
-    <row r="44" spans="3:3">
+    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C44" s="5"/>
     </row>
-    <row r="45" spans="3:3">
+    <row r="45" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C45" s="5"/>
     </row>
-    <row r="46" spans="3:3">
+    <row r="46" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C46" s="5"/>
     </row>
-    <row r="47" spans="3:3">
+    <row r="47" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C47" s="5"/>
     </row>
-    <row r="48" spans="3:3">
+    <row r="48" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C48" s="5"/>
     </row>
-    <row r="49" spans="3:3">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C49" s="5"/>
     </row>
-    <row r="50" spans="3:3">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C50" s="5"/>
     </row>
-    <row r="51" spans="3:3">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C51" s="5"/>
     </row>
-    <row r="52" spans="3:3">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C52" s="5"/>
     </row>
-    <row r="53" spans="3:3">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C53" s="5"/>
     </row>
-    <row r="54" spans="3:3">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C54" s="5"/>
     </row>
-    <row r="55" spans="3:3">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C55" s="5"/>
     </row>
-    <row r="56" spans="3:3">
+    <row r="56" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C56" s="5"/>
     </row>
-    <row r="57" spans="3:3">
+    <row r="57" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C57" s="5"/>
     </row>
-    <row r="58" spans="3:3">
+    <row r="58" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C58" s="5"/>
     </row>
-    <row r="59" spans="3:3">
+    <row r="59" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C59" s="5"/>
     </row>
-    <row r="60" spans="3:3">
+    <row r="60" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C60" s="5"/>
     </row>
-    <row r="61" spans="3:3">
+    <row r="61" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C61" s="5"/>
     </row>
-    <row r="62" spans="3:3">
+    <row r="62" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C62" s="5"/>
     </row>
-    <row r="63" spans="3:3">
+    <row r="63" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C63" s="5"/>
     </row>
-    <row r="64" spans="3:3">
+    <row r="64" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="3:3">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C65" s="5"/>
     </row>
-    <row r="66" spans="3:3">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C66" s="5"/>
     </row>
-    <row r="67" spans="3:3">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C67" s="5"/>
     </row>
-    <row r="68" spans="3:3">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C68" s="5"/>
     </row>
-    <row r="69" spans="3:3">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C69" s="5"/>
     </row>
-    <row r="70" spans="3:3">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C70" s="5"/>
     </row>
-    <row r="71" spans="3:3">
+    <row r="71" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C71" s="5"/>
     </row>
-    <row r="72" spans="3:3">
+    <row r="72" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C72" s="5"/>
     </row>
-    <row r="73" spans="3:3">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C73" s="5"/>
     </row>
-    <row r="74" spans="3:3">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C74" s="5"/>
     </row>
-    <row r="75" spans="3:3">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C75" s="5"/>
     </row>
-    <row r="76" spans="3:3">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C76" s="5"/>
     </row>
-    <row r="77" spans="3:3">
+    <row r="77" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C77" s="5"/>
     </row>
-    <row r="78" spans="3:3">
+    <row r="78" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C78" s="5"/>
     </row>
-    <row r="79" spans="3:3">
+    <row r="79" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C79" s="5"/>
     </row>
-    <row r="80" spans="3:3">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C80" s="5"/>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C81" s="5"/>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C82" s="5"/>
     </row>
-    <row r="83" spans="3:3">
+    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C83" s="5"/>
     </row>
-    <row r="84" spans="3:3">
+    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C84" s="5"/>
     </row>
-    <row r="85" spans="3:3">
+    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C85" s="5"/>
     </row>
-    <row r="86" spans="3:3">
+    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C86" s="5"/>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C87" s="5"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C88" s="5"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C89" s="5"/>
     </row>
-    <row r="90" spans="3:3">
+    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C90" s="5"/>
     </row>
-    <row r="91" spans="3:3">
+    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C91" s="5"/>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C92" s="5"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C93" s="5"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C94" s="5"/>
     </row>
-    <row r="95" spans="3:3">
+    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C95" s="5"/>
     </row>
-    <row r="96" spans="3:3">
+    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C96" s="5"/>
     </row>
-    <row r="97" spans="3:3">
+    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C97" s="5"/>
     </row>
-    <row r="98" spans="3:3">
+    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C98" s="5"/>
     </row>
-    <row r="99" spans="3:3">
+    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C99" s="5"/>
     </row>
-    <row r="100" spans="3:3">
+    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C100" s="5"/>
     </row>
-    <row r="101" spans="3:3">
+    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C101" s="5"/>
     </row>
-    <row r="102" spans="3:3">
+    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C102" s="5"/>
     </row>
-    <row r="103" spans="3:3">
+    <row r="103" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C103" s="5"/>
     </row>
-    <row r="104" spans="3:3">
+    <row r="104" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C104" s="5"/>
     </row>
-    <row r="105" spans="3:3">
+    <row r="105" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C105" s="5"/>
     </row>
-    <row r="106" spans="3:3">
+    <row r="106" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C106" s="5"/>
     </row>
-    <row r="107" spans="3:3">
+    <row r="107" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C107" s="5"/>
     </row>
-    <row r="108" spans="3:3">
+    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C108" s="5"/>
     </row>
-    <row r="109" spans="3:3">
+    <row r="109" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C109" s="5"/>
     </row>
-    <row r="110" spans="3:3">
+    <row r="110" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C110" s="5"/>
     </row>
-    <row r="111" spans="3:3">
+    <row r="111" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C111" s="5"/>
     </row>
-    <row r="112" spans="3:3">
+    <row r="112" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C112" s="5"/>
     </row>
-    <row r="113" spans="3:3">
+    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C113" s="5"/>
     </row>
-    <row r="114" spans="3:3">
+    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C114" s="5"/>
     </row>
-    <row r="115" spans="3:3">
+    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C115" s="5"/>
     </row>
-    <row r="116" spans="3:3">
+    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C116" s="5"/>
     </row>
-    <row r="117" spans="3:3">
+    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C117" s="5"/>
     </row>
-    <row r="118" spans="3:3">
+    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C118" s="5"/>
     </row>
-    <row r="119" spans="3:3">
+    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C119" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C119">
-      <formula1>数据字典!$A$2:$A$3</formula1>
-    </dataValidation>
-  </dataValidations>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>数据字典!$A$2:$A$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C119</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.3727272727273" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.6272727272727" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.7545454545455" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.12727272727273" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.6272727272727" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.6328125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="26.7265625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.453125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.6328125" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1598,7 +1022,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="28" spans="1:7">
+    <row r="3" spans="1:7" ht="28" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>1689306</v>
       </c>
@@ -1615,7 +1039,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>112083174</v>
       </c>
@@ -1630,7 +1054,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" ht="42" spans="1:7">
+    <row r="5" spans="1:7" ht="42" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>2028042</v>
       </c>
@@ -1647,7 +1071,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>166865</v>
       </c>
@@ -1662,57 +1086,63 @@
         <v>16</v>
       </c>
       <c r="F6" s="5">
-        <v>4.7616</v>
+        <v>4.7615999999999996</v>
       </c>
       <c r="G6" s="5"/>
     </row>
-    <row r="8" ht="15" spans="1:1">
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C6">
-      <formula1>数据字典!$A$2:$A$3</formula1>
-    </dataValidation>
-  </dataValidations>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>数据字典!$A$2:$A$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>C3:C6</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.1272727272727" customWidth="1"/>
+    <col min="1" max="1" width="27.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>